--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_3.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01480995812342628</v>
+        <v>0.008198620029558264</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008407479917860684</v>
+        <v>0.008404691819872865</v>
       </c>
       <c r="C2" t="n">
-        <v>19089243</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>19089243</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>14032863</v>
+        <v>4663272</v>
       </c>
       <c r="L2" t="n">
-        <v>8279716</v>
+        <v>2739830</v>
       </c>
       <c r="M2" t="n">
-        <v>2122238</v>
+        <v>695810</v>
       </c>
       <c r="N2" t="n">
-        <v>120036</v>
+        <v>36117</v>
       </c>
       <c r="O2" t="n">
-        <v>1262327</v>
+        <v>419215</v>
       </c>
       <c r="P2" t="n">
-        <v>504876</v>
+        <v>166915</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999920725822449</v>
+        <v>0.999994158744812</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9190739393234253</v>
+        <v>0.9161994457244873</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8310093283653259</v>
+        <v>0.8262661695480347</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7729838490486145</v>
+        <v>0.7740071415901184</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5882848501205444</v>
+        <v>0.5727038979530334</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8249796628952026</v>
+        <v>0.8197639584541321</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8756223917007446</v>
+        <v>0.8764426708221436</v>
       </c>
       <c r="X2" t="n">
-        <v>19089243</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>19089243</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>14599230</v>
+        <v>4849843</v>
       </c>
       <c r="AG2" t="n">
-        <v>8974181</v>
+        <v>2984316</v>
       </c>
       <c r="AH2" t="n">
-        <v>2405464</v>
+        <v>801097</v>
       </c>
       <c r="AI2" t="n">
-        <v>177545</v>
+        <v>59133</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1378044</v>
+        <v>459291</v>
       </c>
       <c r="AK2" t="n">
-        <v>540084</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566497802734375</v>
+        <v>0.9567072987556458</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112433791160583</v>
+        <v>0.9112796187400818</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580086231231689</v>
+        <v>0.8579719662666321</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622910499572754</v>
+        <v>0.6624432802200317</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.90196692943573</v>
+        <v>0.9019978642463684</v>
       </c>
       <c r="AR2" t="n">
         <v>0.9314266443252563</v>
@@ -786,425 +786,425 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.003526585726045928</v>
+        <v>0.001894043184270357</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002014200905435255</v>
+        <v>0.002014117820993523</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>14032863</v>
+        <v>4663272</v>
       </c>
       <c r="E3" t="n">
-        <v>1176812</v>
+        <v>394938</v>
       </c>
       <c r="F3" t="n">
-        <v>28375</v>
+        <v>5108</v>
       </c>
       <c r="G3" t="n">
-        <v>6009</v>
+        <v>849</v>
       </c>
       <c r="H3" t="n">
-        <v>805</v>
+        <v>218</v>
       </c>
       <c r="I3" t="n">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>30288206</v>
+        <v>10069583</v>
       </c>
       <c r="K3" t="n">
-        <v>32897031</v>
+        <v>10925062</v>
       </c>
       <c r="L3" t="n">
-        <v>37832189</v>
+        <v>12560802</v>
       </c>
       <c r="M3" t="n">
-        <v>45949264</v>
+        <v>15278774</v>
       </c>
       <c r="N3" t="n">
-        <v>49025330</v>
+        <v>16299719</v>
       </c>
       <c r="O3" t="n">
-        <v>47581323</v>
+        <v>15814431</v>
       </c>
       <c r="P3" t="n">
-        <v>48725956</v>
+        <v>16199168</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9204924702644348</v>
+        <v>0.9207927584648132</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8395845890045166</v>
+        <v>0.8355404734611511</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7565749287605286</v>
+        <v>0.7449267506599426</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4474580883979797</v>
+        <v>0.4042917490005493</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8258745670318604</v>
+        <v>0.8229600191116333</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8705824613571167</v>
+        <v>0.8634978532791138</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14599230</v>
+        <v>4849843</v>
       </c>
       <c r="Z3" t="n">
-        <v>599197</v>
+        <v>199096</v>
       </c>
       <c r="AA3" t="n">
-        <v>25799</v>
+        <v>8579</v>
       </c>
       <c r="AB3" t="n">
-        <v>20500</v>
+        <v>6817</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30288357</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>33471090</v>
+        <v>11132126</v>
       </c>
       <c r="AG3" t="n">
-        <v>38641818</v>
+        <v>12846342</v>
       </c>
       <c r="AH3" t="n">
-        <v>46174461</v>
+        <v>15349322</v>
       </c>
       <c r="AI3" t="n">
-        <v>49018806</v>
+        <v>16296534</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47699350</v>
+        <v>15856699</v>
       </c>
       <c r="AK3" t="n">
-        <v>48757909</v>
+        <v>16209445</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576436281204224</v>
+        <v>0.9576323628425598</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100050926208496</v>
+        <v>0.9100990891456604</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575446009635925</v>
+        <v>0.8576458692550659</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618342995643616</v>
+        <v>0.6619316339492798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015821814537048</v>
+        <v>0.901633083820343</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312933087348938</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04475454291981733</v>
+        <v>0.0280804847977573</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03183515015025684</v>
+        <v>0.03182526122067923</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1169710</v>
+        <v>403756</v>
       </c>
       <c r="E4" t="n">
-        <v>8279716</v>
+        <v>2739830</v>
       </c>
       <c r="F4" t="n">
-        <v>380092</v>
+        <v>126362</v>
       </c>
       <c r="G4" t="n">
-        <v>10418</v>
+        <v>2791</v>
       </c>
       <c r="H4" t="n">
-        <v>20253</v>
+        <v>6028</v>
       </c>
       <c r="I4" t="n">
-        <v>1490</v>
+        <v>344</v>
       </c>
       <c r="J4" t="n">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="K4" t="n">
-        <v>1235618</v>
+        <v>426528</v>
       </c>
       <c r="L4" t="n">
-        <v>1683729</v>
+        <v>576087</v>
       </c>
       <c r="M4" t="n">
-        <v>623276</v>
+        <v>203161</v>
       </c>
       <c r="N4" t="n">
-        <v>84008</v>
+        <v>26947</v>
       </c>
       <c r="O4" t="n">
-        <v>267804</v>
+        <v>92170</v>
       </c>
       <c r="P4" t="n">
-        <v>71715</v>
+        <v>23531</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999960064888</v>
+        <v>0.999997079372406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9197825789451599</v>
+        <v>0.9184903502464294</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8352749347686768</v>
+        <v>0.8308774828910828</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7646914124488831</v>
+        <v>0.7591885328292847</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5082975625991821</v>
+        <v>0.473982572555542</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8254268765449524</v>
+        <v>0.821358859539032</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8730951547622681</v>
+        <v>0.8699221014976501</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>617717</v>
+        <v>204901</v>
       </c>
       <c r="Z4" t="n">
-        <v>8974181</v>
+        <v>2984316</v>
       </c>
       <c r="AA4" t="n">
-        <v>249583</v>
+        <v>83178</v>
       </c>
       <c r="AB4" t="n">
-        <v>16553</v>
+        <v>5500</v>
       </c>
       <c r="AC4" t="n">
-        <v>3444</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>661559</v>
+        <v>219464</v>
       </c>
       <c r="AG4" t="n">
-        <v>874100</v>
+        <v>290547</v>
       </c>
       <c r="AH4" t="n">
-        <v>398079</v>
+        <v>132613</v>
       </c>
       <c r="AI4" t="n">
-        <v>90532</v>
+        <v>30132</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149777</v>
+        <v>49902</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571464657783508</v>
+        <v>0.9571695923805237</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106237292289734</v>
+        <v>0.9106889963150024</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577765226364136</v>
+        <v>0.8578088283538818</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620625853538513</v>
+        <v>0.6621873378753662</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901774525642395</v>
+        <v>0.9018154144287109</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313599467277527</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>39042</v>
+        <v>13285</v>
       </c>
       <c r="E5" t="n">
-        <v>448724</v>
+        <v>158452</v>
       </c>
       <c r="F5" t="n">
-        <v>2122238</v>
+        <v>695810</v>
       </c>
       <c r="G5" t="n">
-        <v>36427</v>
+        <v>12329</v>
       </c>
       <c r="H5" t="n">
-        <v>150421</v>
+        <v>51863</v>
       </c>
       <c r="I5" t="n">
-        <v>8203</v>
+        <v>2325</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1212088</v>
+        <v>401138</v>
       </c>
       <c r="L5" t="n">
-        <v>1581966</v>
+        <v>539281</v>
       </c>
       <c r="M5" t="n">
-        <v>682822</v>
+        <v>238255</v>
       </c>
       <c r="N5" t="n">
-        <v>148226</v>
+        <v>53217</v>
       </c>
       <c r="O5" t="n">
-        <v>266146</v>
+        <v>90184</v>
       </c>
       <c r="P5" t="n">
-        <v>75053</v>
+        <v>26386</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999969601631165</v>
+        <v>0.9999977350234985</v>
       </c>
       <c r="R5" t="n">
-        <v>0.95042884349823</v>
+        <v>0.9495817422866821</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9338628053665161</v>
+        <v>0.9320560693740845</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9735487699508667</v>
+        <v>0.9731106162071228</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9952967762947083</v>
+        <v>0.9951167106628418</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9891864061355591</v>
+        <v>0.9888917207717896</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9970276355743408</v>
+        <v>0.9969592690467834</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>24202</v>
+        <v>8036</v>
       </c>
       <c r="Z5" t="n">
-        <v>256091</v>
+        <v>85188</v>
       </c>
       <c r="AA5" t="n">
-        <v>2405464</v>
+        <v>801097</v>
       </c>
       <c r="AB5" t="n">
-        <v>29911</v>
+        <v>9959</v>
       </c>
       <c r="AC5" t="n">
-        <v>87493</v>
+        <v>29152</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>645721</v>
+        <v>214567</v>
       </c>
       <c r="AG5" t="n">
-        <v>887501</v>
+        <v>294795</v>
       </c>
       <c r="AH5" t="n">
-        <v>399596</v>
+        <v>132968</v>
       </c>
       <c r="AI5" t="n">
-        <v>90717</v>
+        <v>30201</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150429</v>
+        <v>50108</v>
       </c>
       <c r="AK5" t="n">
-        <v>39845</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973524808883667</v>
+        <v>0.9735605120658875</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964323878288269</v>
+        <v>0.9643431901931763</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838454127311707</v>
+        <v>0.9838218092918396</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963293075561523</v>
+        <v>0.9963247179985046</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939202070236206</v>
+        <v>0.9939077496528625</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983878135681152</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>26739</v>
+        <v>9442</v>
       </c>
       <c r="E6" t="n">
-        <v>38518</v>
+        <v>17247</v>
       </c>
       <c r="F6" t="n">
-        <v>52583</v>
+        <v>16069</v>
       </c>
       <c r="G6" t="n">
-        <v>120036</v>
+        <v>36117</v>
       </c>
       <c r="H6" t="n">
-        <v>27841</v>
+        <v>9654</v>
       </c>
       <c r="I6" t="n">
-        <v>2505</v>
+        <v>784</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19472</v>
+        <v>6471</v>
       </c>
       <c r="Z6" t="n">
-        <v>16132</v>
+        <v>5370</v>
       </c>
       <c r="AA6" t="n">
-        <v>32697</v>
+        <v>10891</v>
       </c>
       <c r="AB6" t="n">
-        <v>177545</v>
+        <v>59133</v>
       </c>
       <c r="AC6" t="n">
-        <v>20973</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>18728</v>
+        <v>5201</v>
       </c>
       <c r="F7" t="n">
-        <v>158158</v>
+        <v>54400</v>
       </c>
       <c r="G7" t="n">
-        <v>29715</v>
+        <v>10501</v>
       </c>
       <c r="H7" t="n">
-        <v>1262327</v>
+        <v>419215</v>
       </c>
       <c r="I7" t="n">
-        <v>59435</v>
+        <v>20055</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2437</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>89010</v>
+        <v>29635</v>
       </c>
       <c r="AB7" t="n">
-        <v>22772</v>
+        <v>7591</v>
       </c>
       <c r="AC7" t="n">
-        <v>1378044</v>
+        <v>459291</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>947</v>
+        <v>249</v>
       </c>
       <c r="F8" t="n">
-        <v>4068</v>
+        <v>1222</v>
       </c>
       <c r="G8" t="n">
-        <v>1439</v>
+        <v>477</v>
       </c>
       <c r="H8" t="n">
-        <v>68484</v>
+        <v>24407</v>
       </c>
       <c r="I8" t="n">
-        <v>504876</v>
+        <v>166915</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>796</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37732</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540084</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
